--- a/FinalProject/Battery Life Estimate/Power Model for TECHIN514.xlsx
+++ b/FinalProject/Battery Life Estimate/Power Model for TECHIN514.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyx/Documents/TECHIN514A-Wi26/FinalProject/Battery Life Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBB6E1F-7AA5-EA4C-AD05-61A813501255}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA16AD7-6634-BF4F-8083-9DFE9EBCFB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -521,7 +521,7 @@
                   <c:v>4.879323361994814E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.267122196064399E-4</c:v>
+                  <c:v>4.2671221960621786E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.4509258287587672E-2</c:v>
@@ -972,7 +972,7 @@
                   <c:v>4.879323361994814E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.267122196064399E-4</c:v>
+                  <c:v>4.2671221960621786E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.4509258287587672E-2</c:v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="O26" s="17">
         <f t="shared" ref="O26:O28" si="0">$M$31/M26</f>
-        <v>52.427184466019419</v>
+        <v>51.897616946160632</v>
       </c>
       <c r="P26" s="16" t="s">
         <v>17</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="0"/>
-        <v>44.909755207811571</v>
+        <v>44.456121316823577</v>
       </c>
       <c r="P27" s="16" t="s">
         <v>17</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="O28" s="17">
         <f t="shared" si="0"/>
-        <v>6.809417975315859</v>
+        <v>6.7406359755651941</v>
       </c>
       <c r="P28" s="16" t="s">
         <v>17</v>
@@ -2130,7 +2130,7 @@
       <c r="K31" s="7"/>
       <c r="M31" s="9">
         <f>B32*B33*B34</f>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>21</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="M33" s="19">
         <f>M31/(E30*M26+F30*M27+G30*M28)</f>
-        <v>1.0186676855630092</v>
+        <v>1.0083781129815648</v>
       </c>
       <c r="N33" s="18" t="s">
         <v>27</v>
@@ -2180,7 +2180,7 @@
         <v>28</v>
       </c>
       <c r="B34" s="11">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I34" s="6"/>
       <c r="K34" s="7"/>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M34" s="19">
         <f>M33*24</f>
-        <v>24.448024453512222</v>
+        <v>24.201074711557553</v>
       </c>
       <c r="N34" s="18" t="s">
         <v>17</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="O62" s="17">
         <f>$M$31/M62</f>
-        <v>1171.1587373568093</v>
+        <v>1159.3288511208818</v>
       </c>
       <c r="P62" s="16" t="s">
         <v>17</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O63" s="17">
         <f>$M$31/M63</f>
-        <v>38.198742785485756</v>
+        <v>37.812896898763682</v>
       </c>
       <c r="P63" s="16" t="s">
         <v>17</v>
@@ -2594,7 +2594,7 @@
       <c r="K66" s="7"/>
       <c r="M66" s="9">
         <f>B67*B68*B69</f>
-        <v>549.45000000000005</v>
+        <v>543.9</v>
       </c>
       <c r="N66" s="9" t="s">
         <v>21</v>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="M68" s="19">
         <f>M66/(E65*M61+F65*M62+G65*M63)</f>
-        <v>1.0693057237019099</v>
+        <v>1.0585046557857289</v>
       </c>
       <c r="N68" s="18" t="s">
         <v>27</v>
@@ -2644,7 +2644,7 @@
         <v>28</v>
       </c>
       <c r="B69" s="11">
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="I69" s="6"/>
       <c r="K69" s="7"/>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="M69" s="19">
         <f>M68*24</f>
-        <v>25.663337368845838</v>
+        <v>25.404111738857495</v>
       </c>
       <c r="N69" s="18" t="s">
         <v>17</v>
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B82" s="23">
         <f>'System Parameters'!B34</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C82" s="9">
         <f>'System Parameters'!C34</f>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B93" s="9">
         <f>B80*B81*B82</f>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="C93" s="9" t="str">
         <f>'System Parameters'!N31</f>
@@ -4730,27 +4730,27 @@
       </c>
       <c r="D93" s="9">
         <f t="shared" ref="D93:I93" si="33">$B93</f>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="E93" s="9">
         <f t="shared" si="33"/>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="F93" s="9">
         <f t="shared" si="33"/>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="G93" s="9">
         <f t="shared" si="33"/>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="H93" s="9">
         <f t="shared" si="33"/>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="I93" s="9">
         <f t="shared" si="33"/>
-        <v>4752</v>
+        <v>4704</v>
       </c>
       <c r="J93" s="9">
         <f>'System Parameters'!O31</f>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B95" s="9">
         <f>B93/($N78*B88+$O78*B89+$P78*B90)</f>
-        <v>1.143264956850409</v>
+        <v>1.1317168259731321</v>
       </c>
       <c r="C95" s="9" t="str">
         <f>'System Parameters'!N33</f>
@@ -4862,27 +4862,27 @@
       </c>
       <c r="D95" s="9">
         <f t="shared" ref="D95:I95" si="34">D93/($N78*D88+$O78*D89+$P78*D90)</f>
-        <v>1.1573524957653856</v>
+        <v>1.1456620665152302</v>
       </c>
       <c r="E95" s="9">
         <f t="shared" si="34"/>
-        <v>1.143320740444538</v>
+        <v>1.1317720460966134</v>
       </c>
       <c r="F95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1437528019777448</v>
+        <v>1.1321997433719089</v>
       </c>
       <c r="G95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1941508321060115</v>
+        <v>1.1820887024887792</v>
       </c>
       <c r="H95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1944726081691468</v>
+        <v>1.1824072282886504</v>
       </c>
       <c r="I95" s="9">
         <f t="shared" si="34"/>
-        <v>1.143264956850409</v>
+        <v>1.1317168259731321</v>
       </c>
       <c r="J95" s="9">
         <f>'System Parameters'!O33</f>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B96" s="9">
         <f>B95*24</f>
-        <v>27.438358964409815</v>
+        <v>27.161203823355169</v>
       </c>
       <c r="C96" s="9" t="str">
         <f>'System Parameters'!N34</f>
@@ -4928,27 +4928,27 @@
       </c>
       <c r="D96" s="9">
         <f t="shared" ref="D96:I96" si="35">D95*24</f>
-        <v>27.776459898369254</v>
+        <v>27.495889596365522</v>
       </c>
       <c r="E96" s="9">
         <f t="shared" si="35"/>
-        <v>27.439697770668914</v>
+        <v>27.162529106318722</v>
       </c>
       <c r="F96" s="9">
         <f t="shared" si="35"/>
-        <v>27.450067247465874</v>
+        <v>27.172793840925813</v>
       </c>
       <c r="G96" s="9">
         <f t="shared" si="35"/>
-        <v>28.659619970544277</v>
+        <v>28.370128859730698</v>
       </c>
       <c r="H96" s="9">
         <f t="shared" si="35"/>
-        <v>28.667342596059523</v>
+        <v>28.377773478927608</v>
       </c>
       <c r="I96" s="9">
         <f t="shared" si="35"/>
-        <v>27.438358964409815</v>
+        <v>27.161203823355169</v>
       </c>
       <c r="J96" s="9">
         <f>'System Parameters'!O34</f>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F98" s="24">
         <f t="shared" si="36"/>
-        <v>4.267122196064399E-4</v>
+        <v>4.2671221960621786E-4</v>
       </c>
       <c r="G98" s="24">
         <f t="shared" si="36"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="B117" s="9">
         <f>'System Parameters'!B69</f>
-        <v>0.99</v>
+        <v>0.98</v>
       </c>
       <c r="C117" s="9">
         <f>'System Parameters'!C69</f>

--- a/FinalProject/Battery Life Estimate/Power Model for TECHIN514.xlsx
+++ b/FinalProject/Battery Life Estimate/Power Model for TECHIN514.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dyx/Documents/TECHIN514A-Wi26/FinalProject/Battery Life Estimate/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AA16AD7-6634-BF4F-8083-9DFE9EBCFB6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CF1AF8C-F472-7444-BFC4-0BEBFCA87774}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="System Parameters" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
                   <c:v>4.879323361994814E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2671221960621786E-4</c:v>
+                  <c:v>4.267122196064399E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.4509258287587672E-2</c:v>
@@ -972,7 +972,7 @@
                   <c:v>4.879323361994814E-5</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>4.2671221960621786E-4</c:v>
+                  <c:v>4.267122196064399E-4</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4.4509258287587672E-2</c:v>
@@ -2030,7 +2030,7 @@
       </c>
       <c r="O26" s="17">
         <f t="shared" ref="O26:O28" si="0">$M$31/M26</f>
-        <v>51.897616946160632</v>
+        <v>48.005295675198589</v>
       </c>
       <c r="P26" s="16" t="s">
         <v>17</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="O27" s="17">
         <f t="shared" si="0"/>
-        <v>44.456121316823577</v>
+        <v>41.121912218061809</v>
       </c>
       <c r="P27" s="16" t="s">
         <v>17</v>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="O28" s="17">
         <f t="shared" si="0"/>
-        <v>6.7406359755651941</v>
+        <v>6.2350882773978036</v>
       </c>
       <c r="P28" s="16" t="s">
         <v>17</v>
@@ -2130,7 +2130,7 @@
       <c r="K31" s="7"/>
       <c r="M31" s="9">
         <f>B32*B33*B34</f>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="N31" s="9" t="s">
         <v>21</v>
@@ -2142,7 +2142,7 @@
         <v>22</v>
       </c>
       <c r="B32" s="13">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="C32" s="9" t="s">
         <v>23</v>
@@ -2156,7 +2156,7 @@
         <v>24</v>
       </c>
       <c r="B33" s="13">
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="C33" s="9" t="s">
         <v>25</v>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="M33" s="19">
         <f>M31/(E30*M26+F30*M27+G30*M28)</f>
-        <v>1.0083781129815648</v>
+        <v>0.93274975450794728</v>
       </c>
       <c r="N33" s="18" t="s">
         <v>27</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="M34" s="19">
         <f>M33*24</f>
-        <v>24.201074711557553</v>
+        <v>22.385994108190737</v>
       </c>
       <c r="N34" s="18" t="s">
         <v>17</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="O62" s="17">
         <f>$M$31/M62</f>
-        <v>1159.3288511208818</v>
+        <v>1072.3791872868157</v>
       </c>
       <c r="P62" s="16" t="s">
         <v>17</v>
@@ -2552,7 +2552,7 @@
       </c>
       <c r="O63" s="17">
         <f>$M$31/M63</f>
-        <v>37.812896898763682</v>
+        <v>34.976929631356406</v>
       </c>
       <c r="P63" s="16" t="s">
         <v>17</v>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="B80" s="14">
         <f>'System Parameters'!B32</f>
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="C80" s="9" t="str">
         <f>'System Parameters'!C32</f>
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B81" s="14">
         <f>'System Parameters'!B33</f>
-        <v>4.8</v>
+        <v>3.7</v>
       </c>
       <c r="C81" s="9" t="str">
         <f>'System Parameters'!C33</f>
@@ -4722,7 +4722,7 @@
       </c>
       <c r="B93" s="9">
         <f>B80*B81*B82</f>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="C93" s="9" t="str">
         <f>'System Parameters'!N31</f>
@@ -4730,27 +4730,27 @@
       </c>
       <c r="D93" s="9">
         <f t="shared" ref="D93:I93" si="33">$B93</f>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="E93" s="9">
         <f t="shared" si="33"/>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="F93" s="9">
         <f t="shared" si="33"/>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="G93" s="9">
         <f t="shared" si="33"/>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="H93" s="9">
         <f t="shared" si="33"/>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="I93" s="9">
         <f t="shared" si="33"/>
-        <v>4704</v>
+        <v>4351.2</v>
       </c>
       <c r="J93" s="9">
         <f>'System Parameters'!O31</f>
@@ -4854,7 +4854,7 @@
       </c>
       <c r="B95" s="9">
         <f>B93/($N78*B88+$O78*B89+$P78*B90)</f>
-        <v>1.1317168259731321</v>
+        <v>1.0468380640251471</v>
       </c>
       <c r="C95" s="9" t="str">
         <f>'System Parameters'!N33</f>
@@ -4862,27 +4862,27 @@
       </c>
       <c r="D95" s="9">
         <f t="shared" ref="D95:I95" si="34">D93/($N78*D88+$O78*D89+$P78*D90)</f>
-        <v>1.1456620665152302</v>
+        <v>1.0597374115265878</v>
       </c>
       <c r="E95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1317720460966134</v>
+        <v>1.0468891426393674</v>
       </c>
       <c r="F95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1321997433719089</v>
+        <v>1.0472847626190158</v>
       </c>
       <c r="G95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1820887024887792</v>
+        <v>1.0934320498021206</v>
       </c>
       <c r="H95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1824072282886504</v>
+        <v>1.0937266861670016</v>
       </c>
       <c r="I95" s="9">
         <f t="shared" si="34"/>
-        <v>1.1317168259731321</v>
+        <v>1.0468380640251471</v>
       </c>
       <c r="J95" s="9">
         <f>'System Parameters'!O33</f>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="B96" s="9">
         <f>B95*24</f>
-        <v>27.161203823355169</v>
+        <v>25.124113536603531</v>
       </c>
       <c r="C96" s="9" t="str">
         <f>'System Parameters'!N34</f>
@@ -4928,27 +4928,27 @@
       </c>
       <c r="D96" s="9">
         <f t="shared" ref="D96:I96" si="35">D95*24</f>
-        <v>27.495889596365522</v>
+        <v>25.433697876638107</v>
       </c>
       <c r="E96" s="9">
         <f t="shared" si="35"/>
-        <v>27.162529106318722</v>
+        <v>25.125339423344819</v>
       </c>
       <c r="F96" s="9">
         <f t="shared" si="35"/>
-        <v>27.172793840925813</v>
+        <v>25.13483430285638</v>
       </c>
       <c r="G96" s="9">
         <f t="shared" si="35"/>
-        <v>28.370128859730698</v>
+        <v>26.242369195250895</v>
       </c>
       <c r="H96" s="9">
         <f t="shared" si="35"/>
-        <v>28.377773478927608</v>
+        <v>26.249440468008039</v>
       </c>
       <c r="I96" s="9">
         <f t="shared" si="35"/>
-        <v>27.161203823355169</v>
+        <v>25.124113536603531</v>
       </c>
       <c r="J96" s="9">
         <f>'System Parameters'!O34</f>
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F98" s="24">
         <f t="shared" si="36"/>
-        <v>4.2671221960621786E-4</v>
+        <v>4.267122196064399E-4</v>
       </c>
       <c r="G98" s="24">
         <f t="shared" si="36"/>
